--- a/client/tests/fixtures/test-orders.xlsx
+++ b/client/tests/fixtures/test-orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YASMINE\Desktop\SaaS Dashboard\client\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDE1D0D-93E7-43BD-ADB8-B136527BD0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8823D22A-6A95-4592-BC42-E69174EEBA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="2200" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
     <t>0666666666</t>
   </si>
   <si>
-    <t>MBP-16-L2</t>
+    <t>MCP-11-K22</t>
   </si>
 </sst>
 </file>
